--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="761">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1727,6 +1727,9 @@
   <si>
     <t>obs-6
 vs-2</t>
+  </si>
+  <si>
+    <t>1792: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2215,6 +2218,9 @@
   <si>
     <t>obs-6
 vs-3</t>
+  </si>
+  <si>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -11207,7 +11213,7 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>84</v>
+        <v>549</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
@@ -11222,7 +11228,7 @@
         <v>137</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11233,14 +11239,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11262,16 +11268,16 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11299,10 +11305,10 @@
         <v>188</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11320,7 +11326,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11344,27 +11350,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11387,19 +11393,19 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11448,7 +11454,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11475,10 +11481,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11489,10 +11495,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11518,13 +11524,13 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11550,13 +11556,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11574,7 +11580,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11598,27 +11604,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11644,16 +11650,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11682,7 +11688,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11700,7 +11706,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11715,7 +11721,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
@@ -11727,10 +11733,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11741,10 +11747,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11767,16 +11773,16 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11826,7 +11832,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11850,27 +11856,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11893,16 +11899,16 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11952,7 +11958,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11967,7 +11973,7 @@
         <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>84</v>
@@ -11976,27 +11982,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12019,19 +12025,19 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12080,7 +12086,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12092,7 +12098,7 @@
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -12107,10 +12113,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12121,10 +12127,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12245,10 +12251,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12371,14 +12377,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12400,10 +12406,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -12458,7 +12464,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12499,10 +12505,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12525,13 +12531,13 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12582,7 +12588,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12591,7 +12597,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -12609,10 +12615,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12623,10 +12629,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12649,13 +12655,13 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12706,7 +12712,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12715,7 +12721,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -12733,10 +12739,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12747,10 +12753,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12776,16 +12782,16 @@
         <v>183</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12813,10 +12819,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12834,7 +12840,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12858,13 +12864,13 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12875,10 +12881,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12904,16 +12910,16 @@
         <v>183</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12938,13 +12944,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12962,7 +12968,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12986,13 +12992,13 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13003,10 +13009,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13029,17 +13035,17 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13088,7 +13094,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13118,7 +13124,7 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13129,10 +13135,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13158,10 +13164,10 @@
         <v>161</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13212,7 +13218,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13239,10 +13245,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13253,10 +13259,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13279,16 +13285,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13338,7 +13344,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13365,10 +13371,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13379,10 +13385,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13405,16 +13411,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13464,7 +13470,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13491,10 +13497,10 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13505,10 +13511,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13531,19 +13537,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13580,7 +13586,7 @@
         <v>84</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
@@ -13590,7 +13596,7 @@
         <v>170</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13602,7 +13608,7 @@
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
@@ -13617,10 +13623,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13631,10 +13637,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13755,10 +13761,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13881,14 +13887,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13910,10 +13916,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13968,7 +13974,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14009,10 +14015,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14038,16 +14044,16 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14096,7 +14102,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -14120,7 +14126,7 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>352</v>
@@ -14137,10 +14143,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14166,13 +14172,13 @@
         <v>437</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>441</v>
@@ -14224,7 +14230,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14233,7 +14239,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -14248,7 +14254,7 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>446</v>
@@ -14265,10 +14271,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14294,13 +14300,13 @@
         <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>545</v>
@@ -14352,7 +14358,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14361,13 +14367,13 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>84</v>
+        <v>704</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>84</v>
@@ -14382,7 +14388,7 @@
         <v>137</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14393,14 +14399,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -14422,16 +14428,16 @@
         <v>183</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14459,10 +14465,10 @@
         <v>188</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14480,7 +14486,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14504,27 +14510,27 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14550,16 +14556,16 @@
         <v>85</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14608,7 +14614,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14635,10 +14641,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14649,13 +14655,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>84</v>
@@ -14677,19 +14683,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14738,7 +14744,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14750,7 +14756,7 @@
         <v>84</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>84</v>
@@ -14765,10 +14771,10 @@
         <v>84</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14779,10 +14785,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14903,10 +14909,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15029,14 +15035,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -15058,10 +15064,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -15116,7 +15122,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15157,10 +15163,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15186,16 +15192,16 @@
         <v>183</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15205,7 +15211,7 @@
         <v>84</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>84</v>
@@ -15244,7 +15250,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>94</v>
@@ -15268,7 +15274,7 @@
         <v>84</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>352</v>
@@ -15285,10 +15291,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15314,13 +15320,13 @@
         <v>451</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>441</v>
@@ -15372,7 +15378,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15381,7 +15387,7 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
@@ -15396,7 +15402,7 @@
         <v>84</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>446</v>
@@ -15413,10 +15419,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15537,10 +15543,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15663,10 +15669,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15765,10 +15771,10 @@
         <v>106</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>84</v>
@@ -15791,10 +15797,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15919,10 +15925,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16045,10 +16051,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16088,7 +16094,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>84</v>
@@ -16171,10 +16177,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16216,7 +16222,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>84</v>
@@ -16299,10 +16305,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16328,13 +16334,13 @@
         <v>183</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>545</v>
@@ -16386,7 +16392,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16395,7 +16401,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16416,7 +16422,7 @@
         <v>137</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16427,14 +16433,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16456,16 +16462,16 @@
         <v>183</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16493,10 +16499,10 @@
         <v>188</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16514,7 +16520,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16538,27 +16544,27 @@
         <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16584,16 +16590,16 @@
         <v>85</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16642,7 +16648,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16669,10 +16675,10 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -16683,13 +16689,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>84</v>
@@ -16711,19 +16717,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16772,7 +16778,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16784,7 +16790,7 @@
         <v>84</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>84</v>
@@ -16799,10 +16805,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16813,10 +16819,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16937,10 +16943,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17063,14 +17069,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -17092,10 +17098,10 @@
         <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>143</v>
@@ -17150,7 +17156,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17191,10 +17197,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17220,16 +17226,16 @@
         <v>183</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17239,7 +17245,7 @@
         <v>84</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>84</v>
@@ -17278,7 +17284,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>94</v>
@@ -17302,7 +17308,7 @@
         <v>84</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>352</v>
@@ -17319,10 +17325,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17348,13 +17354,13 @@
         <v>451</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>441</v>
@@ -17406,7 +17412,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17415,7 +17421,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -17430,7 +17436,7 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>446</v>
@@ -17447,10 +17453,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17571,10 +17577,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17697,10 +17703,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17799,10 +17805,10 @@
         <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>84</v>
@@ -17825,10 +17831,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17953,10 +17959,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18079,10 +18085,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18122,7 +18128,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>84</v>
@@ -18205,10 +18211,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18250,7 +18256,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>84</v>
@@ -18333,10 +18339,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18362,13 +18368,13 @@
         <v>183</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>545</v>
@@ -18420,7 +18426,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18429,7 +18435,7 @@
         <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>106</v>
@@ -18450,7 +18456,7 @@
         <v>137</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18461,14 +18467,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -18490,16 +18496,16 @@
         <v>183</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18527,10 +18533,10 @@
         <v>188</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18548,7 +18554,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18572,27 +18578,27 @@
         <v>84</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18618,16 +18624,16 @@
         <v>85</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18676,7 +18682,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18703,10 +18709,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1729,7 +1729,7 @@
 vs-2</t>
   </si>
   <si>
-    <t>1792: target not supported</t>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2220,7 +2220,7 @@
 vs-3</t>
   </si>
   <si>
-    <t>1793: target not supported</t>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-pulse-oximetry</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-pulse-oximetry</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
+    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1137,7 +1137,7 @@
 </t>
   </si>
   <si>
-    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>Observation.code.coding:PulseOx</t>
@@ -1186,7 +1186,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
+    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1312,7 +1312,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
+    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1334,7 +1334,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1365,7 +1365,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1468,7 +1468,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -1583,7 +1583,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -1849,7 +1849,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1902,7 +1902,7 @@
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
   </si>
   <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -2288,7 +2288,7 @@
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>1239: transform using Split_SpO2_value.Flow() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
+    <t>1239: transform using Split_SpO2_value.Flow() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) case VUID = 4500637</t>
   </si>
   <si>
     <t>Vital.VitalSign.SupplementalO2</t>
@@ -2374,7 +2374,7 @@
     <t>Observation.component:Concentration.value[x].value</t>
   </si>
   <si>
-    <t>1240: transform using Split_SpO2_value.Consentration() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
+    <t>1240: transform using Split_SpO2_value.Consentration() on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (120.5-1.4) case VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].comparator</t>
@@ -2753,7 +2753,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="134.9140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="133.375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1221,6 +1221,9 @@
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.VitalTypeIEN</t>
+  </si>
+  <si>
     <t>Observation.code.coding:PulseOx</t>
   </si>
   <si>
@@ -1270,6 +1273,9 @@
     <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1447,6 +1453,9 @@
   </si>
   <si>
     <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -8367,7 +8376,7 @@
         <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8390,13 +8399,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>384</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8440,7 +8449,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -8520,13 +8529,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>384</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -8570,7 +8579,7 @@
         <v>84</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>84</v>
@@ -8650,10 +8659,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8778,10 +8787,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8804,19 +8813,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8865,7 +8874,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8880,25 +8889,25 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8906,10 +8915,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8932,16 +8941,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8991,7 +9000,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9021,10 +9030,10 @@
         <v>378</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9032,14 +9041,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -9058,19 +9067,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9119,7 +9128,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9140,19 +9149,19 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9160,14 +9169,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -9186,19 +9195,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9235,7 +9244,7 @@
         <v>84</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -9245,7 +9254,7 @@
         <v>143</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9263,10 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -9266,19 +9275,19 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9286,16 +9295,16 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -9314,19 +9323,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9375,7 +9384,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9384,31 +9393,31 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9416,10 +9425,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9442,16 +9451,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9501,7 +9510,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9516,10 +9525,10 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -9528,13 +9537,13 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9542,10 +9551,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9568,17 +9577,17 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9627,7 +9636,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9642,25 +9651,25 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9668,10 +9677,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9694,19 +9703,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9734,16 +9743,16 @@
         <v>214</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -9753,7 +9762,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9762,7 +9771,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9777,30 +9786,30 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -9822,19 +9831,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9862,10 +9871,10 @@
         <v>214</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9883,7 +9892,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9892,7 +9901,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9907,27 +9916,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10048,10 +10057,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10174,10 +10183,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10200,19 +10209,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10261,7 +10270,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10276,10 +10285,10 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>84</v>
@@ -10288,10 +10297,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10302,10 +10311,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10331,20 +10340,20 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>84</v>
@@ -10368,10 +10377,10 @@
         <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -10389,7 +10398,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10416,10 +10425,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10430,10 +10439,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10459,14 +10468,14 @@
         <v>196</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10515,7 +10524,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10542,10 +10551,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10556,10 +10565,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10585,14 +10594,14 @@
         <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10641,7 +10650,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10650,7 +10659,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10668,10 +10677,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10682,10 +10691,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10711,16 +10720,16 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10769,7 +10778,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10784,10 +10793,10 @@
         <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>84</v>
@@ -10796,10 +10805,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10810,10 +10819,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10839,10 +10848,10 @@
         <v>196</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10934,10 +10943,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11056,13 +11065,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>84</v>
@@ -11084,16 +11093,16 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11184,10 +11193,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11308,10 +11317,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11432,10 +11441,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11475,7 +11484,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>84</v>
@@ -11558,10 +11567,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11584,7 +11593,7 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>172</v>
@@ -11602,7 +11611,7 @@
         <v>84</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>84</v>
@@ -11682,10 +11691,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11711,10 +11720,10 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11765,7 +11774,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11806,10 +11815,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11835,16 +11844,16 @@
         <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11872,10 +11881,10 @@
         <v>214</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11893,7 +11902,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11902,13 +11911,13 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>84</v>
@@ -11923,7 +11932,7 @@
         <v>137</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11934,14 +11943,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11963,16 +11972,16 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -12000,10 +12009,10 @@
         <v>214</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -12021,7 +12030,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12045,27 +12054,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12088,19 +12097,19 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12149,7 +12158,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12176,10 +12185,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12190,10 +12199,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12219,13 +12228,13 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12251,13 +12260,13 @@
         <v>84</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12275,7 +12284,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12299,27 +12308,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12345,16 +12354,16 @@
         <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12383,7 +12392,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12401,7 +12410,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12416,7 +12425,7 @@
         <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>84</v>
@@ -12428,10 +12437,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12442,10 +12451,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12468,16 +12477,16 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12527,7 +12536,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12551,27 +12560,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12594,16 +12603,16 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12653,7 +12662,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12677,27 +12686,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12720,19 +12729,19 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12781,7 +12790,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12793,7 +12802,7 @@
         <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -12808,10 +12817,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12822,10 +12831,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12946,10 +12955,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13072,14 +13081,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -13101,10 +13110,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>183</v>
@@ -13159,7 +13168,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13200,10 +13209,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13226,13 +13235,13 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13283,7 +13292,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13292,7 +13301,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -13310,10 +13319,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13324,10 +13333,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13350,13 +13359,13 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13407,16 +13416,16 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI84" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -13434,10 +13443,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13448,10 +13457,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13477,16 +13486,16 @@
         <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13514,10 +13523,10 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>84</v>
@@ -13535,7 +13544,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13559,13 +13568,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13576,10 +13585,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13605,16 +13614,16 @@
         <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13639,13 +13648,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -13663,7 +13672,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13687,13 +13696,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13704,10 +13713,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13730,17 +13739,17 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13789,7 +13798,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13819,7 +13828,7 @@
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13830,10 +13839,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13859,10 +13868,10 @@
         <v>196</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13913,7 +13922,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13940,10 +13949,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13954,10 +13963,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13980,16 +13989,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14039,7 +14048,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14066,10 +14075,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14080,10 +14089,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14106,16 +14115,16 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -14165,7 +14174,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14192,10 +14201,10 @@
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14206,10 +14215,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14232,19 +14241,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14281,7 +14290,7 @@
         <v>84</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
@@ -14291,7 +14300,7 @@
         <v>143</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14303,7 +14312,7 @@
         <v>84</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
@@ -14318,10 +14327,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14332,10 +14341,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14456,10 +14465,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14582,14 +14591,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -14611,10 +14620,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>183</v>
@@ -14669,7 +14678,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14710,10 +14719,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14739,16 +14748,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14797,7 +14806,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -14821,7 +14830,7 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>378</v>
@@ -14838,10 +14847,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14864,19 +14873,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14904,16 +14913,16 @@
         <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -14923,7 +14932,7 @@
         <v>143</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14932,7 +14941,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -14947,30 +14956,30 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>84</v>
@@ -14995,16 +15004,16 @@
         <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15032,10 +15041,10 @@
         <v>214</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>84</v>
@@ -15053,7 +15062,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15062,7 +15071,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -15077,27 +15086,27 @@
         <v>84</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15218,10 +15227,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15344,10 +15353,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15411,7 +15420,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15444,7 +15453,7 @@
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15470,10 +15479,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15598,10 +15607,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15627,16 +15636,16 @@
         <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15664,10 +15673,10 @@
         <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15685,7 +15694,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15694,13 +15703,13 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>84</v>
@@ -15715,7 +15724,7 @@
         <v>137</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15726,14 +15735,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15755,16 +15764,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15792,10 +15801,10 @@
         <v>214</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -15813,7 +15822,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15837,27 +15846,27 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15883,16 +15892,16 @@
         <v>85</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -15941,7 +15950,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15968,10 +15977,10 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -15982,13 +15991,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>84</v>
@@ -16010,19 +16019,19 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16071,7 +16080,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16083,7 +16092,7 @@
         <v>84</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>84</v>
@@ -16098,10 +16107,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -16112,10 +16121,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16236,10 +16245,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16362,14 +16371,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -16391,10 +16400,10 @@
         <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>183</v>
@@ -16449,7 +16458,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16490,10 +16499,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16519,16 +16528,16 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16538,7 +16547,7 @@
         <v>84</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>84</v>
@@ -16577,7 +16586,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>94</v>
@@ -16601,7 +16610,7 @@
         <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>378</v>
@@ -16618,10 +16627,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16644,19 +16653,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16684,10 +16693,10 @@
         <v>214</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16705,7 +16714,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16714,7 +16723,7 @@
         <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>106</v>
@@ -16729,27 +16738,27 @@
         <v>84</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16870,10 +16879,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16996,10 +17005,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17022,19 +17031,19 @@
         <v>95</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17083,7 +17092,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17098,10 +17107,10 @@
         <v>106</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>84</v>
@@ -17110,10 +17119,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17124,10 +17133,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17153,20 +17162,20 @@
         <v>114</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q114" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="R114" t="s" s="2">
         <v>84</v>
@@ -17190,10 +17199,10 @@
         <v>174</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>84</v>
@@ -17211,7 +17220,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17238,10 +17247,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17252,10 +17261,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17281,14 +17290,14 @@
         <v>196</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17337,7 +17346,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17364,10 +17373,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17378,10 +17387,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17407,21 +17416,21 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>84</v>
@@ -17463,7 +17472,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17472,7 +17481,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -17490,10 +17499,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17504,10 +17513,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17533,23 +17542,23 @@
         <v>114</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>84</v>
@@ -17591,7 +17600,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17618,10 +17627,10 @@
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17632,10 +17641,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17661,16 +17670,16 @@
         <v>171</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17698,10 +17707,10 @@
         <v>214</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -17719,7 +17728,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17728,7 +17737,7 @@
         <v>94</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>106</v>
@@ -17749,7 +17758,7 @@
         <v>137</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17760,14 +17769,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17789,16 +17798,16 @@
         <v>171</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17826,10 +17835,10 @@
         <v>214</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>84</v>
@@ -17847,7 +17856,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17871,27 +17880,27 @@
         <v>84</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17917,16 +17926,16 @@
         <v>85</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -17975,7 +17984,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -18002,10 +18011,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -18016,13 +18025,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>84</v>
@@ -18044,19 +18053,19 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18105,7 +18114,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18117,7 +18126,7 @@
         <v>84</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>84</v>
@@ -18132,10 +18141,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18146,10 +18155,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18270,10 +18279,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18396,14 +18405,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18425,10 +18434,10 @@
         <v>139</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>183</v>
@@ -18483,7 +18492,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18524,10 +18533,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18553,16 +18562,16 @@
         <v>171</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18572,7 +18581,7 @@
         <v>84</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>84</v>
@@ -18611,7 +18620,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>94</v>
@@ -18635,7 +18644,7 @@
         <v>84</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>378</v>
@@ -18652,10 +18661,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18678,19 +18687,19 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18718,10 +18727,10 @@
         <v>214</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18739,7 +18748,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18748,7 +18757,7 @@
         <v>94</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>106</v>
@@ -18763,27 +18772,27 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18904,10 +18913,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19030,10 +19039,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19056,19 +19065,19 @@
         <v>95</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19117,7 +19126,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19132,10 +19141,10 @@
         <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>84</v>
@@ -19144,10 +19153,10 @@
         <v>84</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19158,10 +19167,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19187,20 +19196,20 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q130" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="R130" t="s" s="2">
         <v>84</v>
@@ -19224,10 +19233,10 @@
         <v>174</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19245,7 +19254,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19272,10 +19281,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
@@ -19286,10 +19295,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19315,14 +19324,14 @@
         <v>196</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19371,7 +19380,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19398,10 +19407,10 @@
         <v>84</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
@@ -19412,10 +19421,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19441,21 +19450,21 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>84</v>
@@ -19497,7 +19506,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19506,7 +19515,7 @@
         <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19524,10 +19533,10 @@
         <v>84</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
@@ -19538,10 +19547,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19567,23 +19576,23 @@
         <v>114</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>84</v>
@@ -19625,7 +19634,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19652,10 +19661,10 @@
         <v>84</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -19666,10 +19675,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19695,16 +19704,16 @@
         <v>171</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -19732,10 +19741,10 @@
         <v>214</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -19753,7 +19762,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -19762,7 +19771,7 @@
         <v>94</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>106</v>
@@ -19783,7 +19792,7 @@
         <v>137</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -19794,14 +19803,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19823,16 +19832,16 @@
         <v>171</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -19860,10 +19869,10 @@
         <v>214</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>84</v>
@@ -19881,7 +19890,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -19905,27 +19914,27 @@
         <v>84</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19951,16 +19960,16 @@
         <v>85</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -20009,7 +20018,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>82</v>
@@ -20036,10 +20045,10 @@
         <v>84</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$173</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7016" uniqueCount="833">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2259,42 +2259,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2365,7 +2329,13 @@
     <t>Observation.component:FlowRate.value[x].id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.value[x].value</t>
@@ -2485,6 +2455,168 @@
   </si>
   <si>
     <t>Observation.component:Concentration.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition</t>
+  </si>
+  <si>
+    <t>va-pre-condition</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+  </si>
+  <si>
+    <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+  </si>
+  <si>
+    <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size</t>
+  </si>
+  <si>
+    <t>va-cuff-size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2801,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR136"/>
+  <dimension ref="A1:AR173"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -2829,7 +2961,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2839,7 +2971,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="144.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -14922,14 +15054,16 @@
         <v>84</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AC96" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>711</v>
@@ -14976,11 +15110,9 @@
         <v>717</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>84</v>
       </c>
@@ -14998,22 +15130,22 @@
         <v>84</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>470</v>
+        <v>564</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15041,10 +15173,10 @@
         <v>214</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>471</v>
+        <v>565</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>472</v>
+        <v>566</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>84</v>
@@ -15062,7 +15194,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15071,13 +15203,13 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>84</v>
+        <v>722</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>84</v>
@@ -15086,38 +15218,38 @@
         <v>84</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>475</v>
+        <v>137</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>476</v>
+        <v>569</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>84</v>
@@ -15129,16 +15261,20 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>153</v>
+        <v>572</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
       </c>
@@ -15162,13 +15298,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>84</v>
+        <v>577</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15186,19 +15322,19 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>155</v>
+        <v>723</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>84</v>
@@ -15210,31 +15346,31 @@
         <v>84</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>84</v>
+        <v>578</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>84</v>
+        <v>579</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>157</v>
+        <v>580</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>84</v>
+        <v>581</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15253,18 +15389,20 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>198</v>
+        <v>725</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>199</v>
+        <v>726</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15300,19 +15438,19 @@
         <v>84</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>161</v>
+        <v>724</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15324,7 +15462,7 @@
         <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15339,10 +15477,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>84</v>
+        <v>635</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>157</v>
+        <v>636</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15353,12 +15491,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15367,7 +15507,7 @@
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>95</v>
@@ -15379,19 +15519,19 @@
         <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>302</v>
+        <v>629</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>303</v>
+        <v>729</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>304</v>
+        <v>730</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>305</v>
+        <v>696</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>306</v>
+        <v>697</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15416,11 +15556,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>725</v>
+        <v>84</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15438,7 +15580,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>307</v>
+        <v>694</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15450,10 +15592,10 @@
         <v>84</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>699</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>726</v>
+        <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15465,10 +15607,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>308</v>
+        <v>700</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>309</v>
+        <v>701</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15479,10 +15621,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>728</v>
+        <v>702</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15502,23 +15644,19 @@
         <v>84</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>84</v>
       </c>
@@ -15566,7 +15704,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15578,7 +15716,7 @@
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15593,10 +15731,10 @@
         <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
@@ -15607,24 +15745,24 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>84</v>
@@ -15633,20 +15771,18 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>730</v>
+        <v>198</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>731</v>
+        <v>199</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>84</v>
       </c>
@@ -15670,13 +15806,13 @@
         <v>84</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15694,22 +15830,22 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>729</v>
+        <v>161</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>733</v>
+        <v>84</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>734</v>
+        <v>84</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>84</v>
@@ -15721,10 +15857,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15735,14 +15871,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>571</v>
+        <v>640</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -15755,25 +15891,25 @@
         <v>84</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>572</v>
+        <v>641</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>573</v>
+        <v>642</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>575</v>
+        <v>184</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15798,13 +15934,13 @@
         <v>84</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>576</v>
+        <v>84</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>577</v>
+        <v>84</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -15822,7 +15958,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>735</v>
+        <v>643</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15834,7 +15970,7 @@
         <v>84</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -15846,27 +15982,27 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>580</v>
+        <v>137</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15874,34 +16010,34 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -15911,7 +16047,7 @@
         <v>84</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>84</v>
+        <v>735</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>84</v>
@@ -15926,13 +16062,13 @@
         <v>84</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>84</v>
@@ -15950,13 +16086,13 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>84</v>
@@ -15974,16 +16110,16 @@
         <v>84</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>84</v>
+        <v>710</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>635</v>
+        <v>378</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>636</v>
+        <v>379</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>84</v>
@@ -15991,14 +16127,12 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>740</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>84</v>
       </c>
@@ -16019,19 +16153,19 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>629</v>
+        <v>480</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>741</v>
+        <v>712</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>696</v>
+        <v>714</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>697</v>
+        <v>470</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16056,13 +16190,13 @@
         <v>84</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>84</v>
@@ -16080,19 +16214,19 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>84</v>
+        <v>715</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>699</v>
+        <v>106</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>84</v>
@@ -16104,27 +16238,27 @@
         <v>84</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>84</v>
+        <v>716</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>700</v>
+        <v>475</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>701</v>
+        <v>476</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>702</v>
+        <v>738</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16245,10 +16379,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>703</v>
+        <v>740</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16318,16 +16452,16 @@
         <v>84</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>161</v>
@@ -16371,45 +16505,45 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>704</v>
+        <v>742</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>640</v>
+        <v>84</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J108" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>641</v>
+        <v>488</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>642</v>
+        <v>489</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>183</v>
+        <v>490</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>184</v>
+        <v>491</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16458,25 +16592,25 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>643</v>
+        <v>492</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>84</v>
+        <v>743</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>84</v>
+        <v>744</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16485,10 +16619,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>137</v>
+        <v>496</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16499,10 +16633,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16510,44 +16644,44 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I109" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>706</v>
+        <v>499</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>709</v>
+        <v>501</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q109" s="2"/>
+      <c r="Q109" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="R109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>747</v>
+        <v>84</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>84</v>
@@ -16562,13 +16696,13 @@
         <v>84</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>374</v>
+        <v>503</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>375</v>
+        <v>504</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>84</v>
@@ -16586,10 +16720,10 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>705</v>
+        <v>505</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>94</v>
@@ -16610,16 +16744,16 @@
         <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>710</v>
+        <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>378</v>
+        <v>506</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>379</v>
+        <v>507</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>84</v>
@@ -16627,10 +16761,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16638,7 +16772,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>94</v>
@@ -16653,19 +16787,17 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>480</v>
+        <v>196</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>712</v>
+        <v>510</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>714</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16690,13 +16822,13 @@
         <v>84</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>472</v>
+        <v>84</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>84</v>
@@ -16714,7 +16846,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>711</v>
+        <v>513</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16723,7 +16855,7 @@
         <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>715</v>
+        <v>84</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>106</v>
@@ -16738,19 +16870,19 @@
         <v>84</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" hidden="true">
@@ -16758,7 +16890,7 @@
         <v>749</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16766,37 +16898,39 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>153</v>
+        <v>518</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>154</v>
+        <v>519</v>
       </c>
       <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>84</v>
+        <v>751</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>84</v>
@@ -16838,7 +16972,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>155</v>
+        <v>521</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16847,10 +16981,10 @@
         <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>84</v>
@@ -16865,10 +16999,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>157</v>
+        <v>523</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16879,50 +17013,52 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>722</v>
+        <v>753</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>198</v>
+        <v>526</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>199</v>
+        <v>527</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>84</v>
+        <v>754</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>84</v>
@@ -16952,31 +17088,31 @@
         <v>84</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>161</v>
+        <v>530</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>84</v>
@@ -16991,10 +17127,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>157</v>
+        <v>532</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17005,10 +17141,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>752</v>
+        <v>717</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17016,7 +17152,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>94</v>
@@ -17028,22 +17164,22 @@
         <v>84</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>487</v>
+        <v>171</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>488</v>
+        <v>718</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>489</v>
+        <v>719</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>490</v>
+        <v>720</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17068,13 +17204,13 @@
         <v>84</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>84</v>
@@ -17092,7 +17228,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>492</v>
+        <v>717</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17101,16 +17237,16 @@
         <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>84</v>
+        <v>721</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>753</v>
+        <v>84</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>754</v>
+        <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>84</v>
@@ -17119,10 +17255,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>495</v>
+        <v>137</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>496</v>
+        <v>569</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17133,50 +17269,50 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>499</v>
+        <v>572</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="O114" t="s" s="2">
-        <v>501</v>
+        <v>575</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q114" t="s" s="2">
-        <v>502</v>
-      </c>
+      <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
         <v>84</v>
       </c>
@@ -17196,13 +17332,13 @@
         <v>84</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>503</v>
+        <v>576</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>84</v>
@@ -17220,13 +17356,13 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>505</v>
+        <v>723</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>84</v>
@@ -17244,19 +17380,19 @@
         <v>84</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>84</v>
+        <v>578</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>506</v>
+        <v>579</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>84</v>
+        <v>581</v>
       </c>
     </row>
     <row r="115" hidden="true">
@@ -17264,7 +17400,7 @@
         <v>757</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17272,32 +17408,34 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>510</v>
+        <v>725</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>726</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="O115" t="s" s="2">
-        <v>512</v>
+        <v>633</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17346,13 +17484,13 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>513</v>
+        <v>724</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>84</v>
@@ -17373,10 +17511,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>514</v>
+        <v>635</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>515</v>
+        <v>636</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17387,18 +17525,20 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="B116" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>94</v>
@@ -17413,24 +17553,26 @@
         <v>95</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>108</v>
+        <v>629</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>518</v>
+        <v>760</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O116" t="s" s="2">
-        <v>520</v>
+        <v>697</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>761</v>
+        <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>84</v>
@@ -17472,19 +17614,19 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>521</v>
+        <v>694</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>106</v>
+        <v>699</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>84</v>
@@ -17499,10 +17641,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>514</v>
+        <v>700</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>523</v>
+        <v>701</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17513,10 +17655,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>763</v>
+        <v>702</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17524,41 +17666,37 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>526</v>
+        <v>153</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>764</v>
+        <v>84</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>84</v>
@@ -17600,7 +17738,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>530</v>
+        <v>155</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17612,7 +17750,7 @@
         <v>84</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>84</v>
@@ -17627,10 +17765,10 @@
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>514</v>
+        <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>532</v>
+        <v>157</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17641,24 +17779,24 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>84</v>
@@ -17667,20 +17805,18 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>730</v>
+        <v>198</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>731</v>
+        <v>199</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>84</v>
       </c>
@@ -17704,13 +17840,13 @@
         <v>84</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -17728,19 +17864,19 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>729</v>
+        <v>161</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>733</v>
+        <v>84</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>84</v>
@@ -17755,10 +17891,10 @@
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17769,14 +17905,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>571</v>
+        <v>640</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17789,25 +17925,25 @@
         <v>84</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>572</v>
+        <v>641</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>573</v>
+        <v>642</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>575</v>
+        <v>184</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17832,13 +17968,13 @@
         <v>84</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>576</v>
+        <v>84</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>577</v>
+        <v>84</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>84</v>
@@ -17856,7 +17992,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>735</v>
+        <v>643</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17868,7 +18004,7 @@
         <v>84</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>84</v>
@@ -17880,27 +18016,27 @@
         <v>84</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>580</v>
+        <v>137</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17908,34 +18044,34 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -17945,7 +18081,7 @@
         <v>84</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>84</v>
+        <v>765</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>84</v>
@@ -17960,13 +18096,13 @@
         <v>84</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>84</v>
@@ -17984,13 +18120,13 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>84</v>
@@ -18008,16 +18144,16 @@
         <v>84</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>84</v>
+        <v>710</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>635</v>
+        <v>378</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>636</v>
+        <v>379</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>84</v>
@@ -18025,14 +18161,12 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>769</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>84</v>
       </c>
@@ -18053,19 +18187,19 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>629</v>
+        <v>480</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>770</v>
+        <v>712</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>696</v>
+        <v>714</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>697</v>
+        <v>470</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18090,13 +18224,13 @@
         <v>84</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18114,19 +18248,19 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>84</v>
+        <v>715</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>699</v>
+        <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>84</v>
@@ -18138,27 +18272,27 @@
         <v>84</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>84</v>
+        <v>716</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>700</v>
+        <v>475</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>701</v>
+        <v>476</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>702</v>
+        <v>738</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18279,10 +18413,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>703</v>
+        <v>740</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18352,16 +18486,16 @@
         <v>84</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF123" t="s" s="2">
         <v>161</v>
@@ -18405,45 +18539,45 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>704</v>
+        <v>742</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>640</v>
+        <v>84</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>139</v>
+        <v>487</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>641</v>
+        <v>488</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>642</v>
+        <v>489</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>183</v>
+        <v>490</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>184</v>
+        <v>491</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18492,25 +18626,25 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>643</v>
+        <v>492</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>84</v>
+        <v>770</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>84</v>
+        <v>744</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>84</v>
@@ -18519,10 +18653,10 @@
         <v>84</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>137</v>
+        <v>496</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18533,10 +18667,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18544,44 +18678,44 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I125" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>706</v>
+        <v>499</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>709</v>
+        <v>501</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q125" s="2"/>
+      <c r="Q125" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="R125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>775</v>
+        <v>84</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>84</v>
@@ -18596,13 +18730,13 @@
         <v>84</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>374</v>
+        <v>503</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>375</v>
+        <v>504</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18620,10 +18754,10 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>705</v>
+        <v>505</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>94</v>
@@ -18644,16 +18778,16 @@
         <v>84</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>710</v>
+        <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>378</v>
+        <v>506</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>379</v>
+        <v>507</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>84</v>
@@ -18661,10 +18795,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>711</v>
+        <v>748</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18672,7 +18806,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>94</v>
@@ -18687,19 +18821,17 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>480</v>
+        <v>196</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>712</v>
+        <v>510</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>714</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18724,13 +18856,13 @@
         <v>84</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>472</v>
+        <v>84</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18748,7 +18880,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>711</v>
+        <v>513</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18757,7 +18889,7 @@
         <v>94</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>715</v>
+        <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>106</v>
@@ -18772,27 +18904,27 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18800,37 +18932,39 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>153</v>
+        <v>518</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>154</v>
+        <v>519</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>84</v>
+        <v>751</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>84</v>
@@ -18872,7 +19006,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>155</v>
+        <v>521</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18881,10 +19015,10 @@
         <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>84</v>
@@ -18899,10 +19033,10 @@
         <v>84</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>157</v>
+        <v>523</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18913,50 +19047,52 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>722</v>
+        <v>753</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>198</v>
+        <v>526</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>199</v>
+        <v>527</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>84</v>
+        <v>775</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>84</v>
@@ -18986,31 +19122,31 @@
         <v>84</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>161</v>
+        <v>530</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>84</v>
@@ -19025,10 +19161,10 @@
         <v>84</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>157</v>
+        <v>532</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19039,10 +19175,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>752</v>
+        <v>717</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19050,7 +19186,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>94</v>
@@ -19062,22 +19198,22 @@
         <v>84</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>487</v>
+        <v>171</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>488</v>
+        <v>718</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>489</v>
+        <v>719</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>490</v>
+        <v>720</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19102,13 +19238,13 @@
         <v>84</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>84</v>
@@ -19126,7 +19262,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>492</v>
+        <v>717</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19135,16 +19271,16 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>84</v>
+        <v>721</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>780</v>
+        <v>84</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>754</v>
+        <v>84</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>84</v>
@@ -19153,10 +19289,10 @@
         <v>84</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>495</v>
+        <v>137</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>496</v>
+        <v>569</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19167,50 +19303,50 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>499</v>
+        <v>572</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="O130" t="s" s="2">
-        <v>501</v>
+        <v>575</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q130" t="s" s="2">
-        <v>502</v>
-      </c>
+      <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
         <v>84</v>
       </c>
@@ -19230,13 +19366,13 @@
         <v>84</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>503</v>
+        <v>576</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19254,13 +19390,13 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>505</v>
+        <v>723</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>84</v>
@@ -19278,27 +19414,27 @@
         <v>84</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>84</v>
+        <v>578</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>506</v>
+        <v>579</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>84</v>
+        <v>581</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>758</v>
+        <v>724</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19306,32 +19442,34 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>510</v>
+        <v>725</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>726</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="O131" t="s" s="2">
-        <v>512</v>
+        <v>633</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19380,13 +19518,13 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>513</v>
+        <v>724</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>84</v>
@@ -19407,10 +19545,10 @@
         <v>84</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>514</v>
+        <v>635</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>515</v>
+        <v>636</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
@@ -19421,18 +19559,20 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>780</v>
+      </c>
       <c r="D132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>94</v>
@@ -19447,24 +19587,26 @@
         <v>95</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>108</v>
+        <v>629</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>518</v>
+        <v>695</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>696</v>
+      </c>
       <c r="O132" t="s" s="2">
-        <v>520</v>
+        <v>697</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>761</v>
+        <v>84</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>84</v>
@@ -19506,19 +19648,19 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>521</v>
+        <v>694</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>106</v>
+        <v>699</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>84</v>
@@ -19533,10 +19675,10 @@
         <v>84</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>514</v>
+        <v>700</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>523</v>
+        <v>701</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
@@ -19547,10 +19689,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>763</v>
+        <v>702</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19558,41 +19700,37 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>526</v>
+        <v>153</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>785</v>
+        <v>84</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>84</v>
@@ -19634,7 +19772,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>530</v>
+        <v>155</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19646,7 +19784,7 @@
         <v>84</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>84</v>
@@ -19661,10 +19799,10 @@
         <v>84</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>514</v>
+        <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>532</v>
+        <v>157</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -19675,24 +19813,24 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>84</v>
@@ -19701,20 +19839,18 @@
         <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>730</v>
+        <v>198</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>731</v>
+        <v>199</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>84</v>
       </c>
@@ -19738,13 +19874,13 @@
         <v>84</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -19762,19 +19898,19 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>729</v>
+        <v>161</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>733</v>
+        <v>84</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>84</v>
@@ -19789,10 +19925,10 @@
         <v>84</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -19803,14 +19939,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>571</v>
+        <v>640</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -19823,25 +19959,25 @@
         <v>84</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>572</v>
+        <v>641</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>573</v>
+        <v>642</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>575</v>
+        <v>184</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -19866,13 +20002,13 @@
         <v>84</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>576</v>
+        <v>84</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>577</v>
+        <v>84</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>84</v>
@@ -19890,7 +20026,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>735</v>
+        <v>643</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -19902,7 +20038,7 @@
         <v>84</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>84</v>
@@ -19914,27 +20050,27 @@
         <v>84</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>579</v>
+        <v>84</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>580</v>
+        <v>137</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19942,34 +20078,34 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -19994,13 +20130,13 @@
         <v>84</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>84</v>
@@ -20018,13 +20154,13 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>84</v>
@@ -20042,23 +20178,4727 @@
         <v>84</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>84</v>
+        <v>710</v>
       </c>
       <c r="AO136" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR136" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AC137" s="2"/>
+      <c r="AD137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR137" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR138" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR139" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP140" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR140" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y141" s="2"/>
+      <c r="Z141" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP141" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR141" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP142" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR142" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP143" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AQ143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR143" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AP144" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AQ144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR144" t="s" s="2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO145" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AP136" t="s" s="2">
+      <c r="AP145" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AQ136" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR136" t="s" s="2">
+      <c r="AQ145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR145" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR146" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR147" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP148" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR148" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP149" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR149" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP150" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ150" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR150" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AC151" s="2"/>
+      <c r="AD151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP151" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR151" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR152" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP153" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR153" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP154" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR154" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y155" s="2"/>
+      <c r="Z155" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP155" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR155" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR156" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="P157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP157" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AQ157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR157" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AP158" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AQ158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR158" t="s" s="2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AP159" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AQ159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR159" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="160" hidden="true">
+      <c r="A160" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="P160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AP160" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AQ160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR160" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" hidden="true">
+      <c r="A161" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP161" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR161" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP162" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR162" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="163" hidden="true">
+      <c r="A163" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP163" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR163" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="164" hidden="true">
+      <c r="A164" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="P164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO164" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP164" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ164" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AR164" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="165" hidden="true">
+      <c r="A165" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AC165" s="2"/>
+      <c r="AD165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP165" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR165" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="166" hidden="true">
+      <c r="A166" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="D166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP166" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AQ166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR166" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR167" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP168" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR168" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y169" s="2"/>
+      <c r="Z169" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR169" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR170" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AQ171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR171" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AQ172" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR172" t="s" s="2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AQ173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR173" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR136">
+  <autoFilter ref="A1:AR173">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20068,7 +24908,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI135">
+  <conditionalFormatting sqref="A2:AI172">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>660-1: fixed value = http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
+++ b/docs/StructureDefinition-VitalSignsSpO2Observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
